--- a/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Função EXT.TEXTO.xlsx
+++ b/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Função EXT.TEXTO.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ALUNOS_FIC\LINELSON.ALUNOS\pastas\3 - FUNÇÕES DE TEXTO E DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\3 - FUNÇÕES DE TEXTO E DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDC7E4C-7E51-4960-BB3F-4B0B5B67FC48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB75BDCE-A765-4505-BB74-45BB83C7B547}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -475,45 +475,90 @@
         <v>2</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="C3" s="4" t="str">
+        <f>MID(A3,1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="str">
+        <f>MID(A3,2,3)</f>
+        <v>CPD</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f>MID(A3,5,2)</f>
+        <v>SP</v>
+      </c>
     </row>
     <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="4" t="str">
+        <f t="shared" ref="C4:C7" si="0">MID(A4,1,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="str">
+        <f t="shared" ref="D4:D7" si="1">MID(A4,2,3)</f>
+        <v>VEN</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" ref="E4:E7" si="2">MID(A4,5,2)</f>
+        <v>RJ</v>
+      </c>
     </row>
     <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="C5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>CPD</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>SP</v>
+      </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>VEN</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>SP</v>
+      </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="C7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>ADM</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>SP</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
@@ -540,8 +585,14 @@
         <v>10</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="4" t="str">
+        <f>MID($A10,1,4)</f>
+        <v>1234</v>
+      </c>
+      <c r="D10" s="4" t="str">
+        <f>MID($A10,6,10)</f>
+        <v>Noruega</v>
+      </c>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -549,8 +600,14 @@
         <v>11</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="C11" s="4" t="str">
+        <f t="shared" ref="C11:C13" si="3">MID($A11,1,4)</f>
+        <v>7898</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f t="shared" ref="D11:D13" si="4">MID($A11,6,10)</f>
+        <v>Brasil</v>
+      </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -558,8 +615,14 @@
         <v>12</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>4455</v>
+      </c>
+      <c r="D12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>Itália</v>
+      </c>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -567,8 +630,14 @@
         <v>13</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="C13" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>3333</v>
+      </c>
+      <c r="D13" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>Canadá</v>
+      </c>
       <c r="E13" s="5"/>
     </row>
   </sheetData>
